--- a/tabelas/2026.xlsx
+++ b/tabelas/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\narrativapilotodois-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4CFE217-B4B5-4B0B-9157-7FF77FDBE424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD2095EE-D46C-4C8A-AA40-421E786552DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="208">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -640,6 +640,15 @@
   </si>
   <si>
     <t>08.779.141.0190.001</t>
+  </si>
+  <si>
+    <t>08.779.141.0190.002</t>
+  </si>
+  <si>
+    <t>08.779.141.0190.003</t>
+  </si>
+  <si>
+    <t>08.779.141.0190.004</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FEC8DEA-D1AE-4B91-B66D-48CA0A2026FB}">
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -4840,18 +4849,15 @@
       <c r="H117" s="2">
         <v>0</v>
       </c>
-      <c r="I117" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="J117" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="K117" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="4" t="s">
         <v>197</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -4867,22 +4873,22 @@
         <v>9</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G118" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H118" s="2">
-        <v>0</v>
+        <v>158.94</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="J118" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="K118" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -4950,14 +4956,14 @@
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="4" t="s">
         <v>203</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>200</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>10</v>
@@ -4972,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="J121" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="K121" t="s">
         <v>31</v>
@@ -4989,7 +4995,7 @@
         <v>200</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E122" s="3" t="s">
         <v>10</v>
@@ -5001,15 +5007,120 @@
         <v>2026</v>
       </c>
       <c r="H122" s="2">
-        <v>350.91</v>
+        <v>150.44999999999999</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J122" t="s">
-        <v>103</v>
-      </c>
-      <c r="K122" t="s">
+        <v>51</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G123" s="2">
+        <v>2026</v>
+      </c>
+      <c r="H123" s="2">
+        <v>45.56</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G124" s="2">
+        <v>2026</v>
+      </c>
+      <c r="H124" s="2">
+        <v>170.89</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G125" s="2">
+        <v>2026</v>
+      </c>
+      <c r="H125" s="2">
+        <v>205.78</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K125" s="2" t="s">
         <v>30</v>
       </c>
     </row>

--- a/tabelas/2026.xlsx
+++ b/tabelas/2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Acadêmico Juliano Zanoni\Engenharia de Software\Projetos Engenharia\Projetos\narrativapilotodois-portfolio\tabelas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD2095EE-D46C-4C8A-AA40-421E786552DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF3316C6-8CB6-44DF-B443-73DEDD413D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{349979B7-C21B-407A-A293-DC1F6033EF36}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="209">
   <si>
     <t>INSCRICAO</t>
   </si>
@@ -649,6 +649,9 @@
   </si>
   <si>
     <t>08.779.141.0190.004</t>
+  </si>
+  <si>
+    <t>08.779.141.0170.001</t>
   </si>
 </sst>
 </file>
@@ -4858,10 +4861,10 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>200</v>
